--- a/dataset/construct/dataset_splits/data_size/2_percent/lmu/fold4.xlsx
+++ b/dataset/construct/dataset_splits/data_size/2_percent/lmu/fold4.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN3"/>
+  <dimension ref="A1:AK3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,185 +446,170 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>BMI</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>BMI</t>
+          <t>AFPRE</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CABGPRE</t>
+          <t>LVEFPRE</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>AFPRE</t>
+          <t>PREDILATION</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>LVEFPRE</t>
+          <t>CT_ValScNCC</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>NTPROBNPPRE</t>
+          <t>CT_ValScRCC</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>PREDILATION</t>
+          <t>CT_ValScLCC</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScNCC</t>
+          <t>CT_ValvScTot</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScRCC</t>
+          <t>CT_AnnScNCC</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScLCC</t>
+          <t>CT_AnnScRCC</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValvScTot</t>
+          <t>CT_AnnScLCC</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScNCC</t>
+          <t>CT_AnnScTot</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScRCC</t>
+          <t>CT_LVOTScNCC</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScLCC</t>
+          <t>CT_LVOTScRCC</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScTot</t>
+          <t>CT_LVOTScLCC</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScNCC</t>
+          <t>CT_LVOTScTot</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScRCC</t>
+          <t>SEX</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScLCC</t>
+          <t>CT_AnnMean</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScTot</t>
+          <t>ECC_INDEX</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>CT_Peri_Deri</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnMean</t>
+          <t>CT_Area_Deri</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>ECC_INDEX</t>
+          <t>nyha2</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>CT_Peri_Deri</t>
+          <t>nyha3</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>CT_Area_Deri</t>
+          <t>nyha4</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>nyha2</t>
+          <t>model1</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>nyha3</t>
+          <t>model2</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>nyha4</t>
+          <t>model3</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>model1</t>
+          <t>model4</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>model2</t>
+          <t>model7</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>model3</t>
+          <t>model8</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>model4</t>
+          <t>brand2</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>model7</t>
+          <t>brand8</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>model8</t>
+          <t>QRSADM</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>brand2</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>brand8</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>QRSADM</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>PQADM</t>
         </is>
@@ -632,7 +617,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>53336915</v>
+        <v>54153818</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -640,117 +625,106 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>81.8945927446954</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
+        <v>79.7891854893908</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.6293520742945</v>
+      </c>
       <c r="E2" t="n">
-        <v>27.6360544217687</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>60</v>
+      </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="n">
-        <v>55</v>
-      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>204</v>
-      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="M2" t="n">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="N2" t="n">
-        <v>565</v>
+        <v>116</v>
       </c>
       <c r="O2" t="n">
-        <v>202</v>
+        <v>504</v>
       </c>
       <c r="P2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>381</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>23.6</v>
       </c>
       <c r="V2" t="n">
-        <v>190</v>
+        <v>0.22</v>
       </c>
       <c r="W2" t="n">
-        <v>2</v>
+        <v>24.28704431582323</v>
       </c>
       <c r="X2" t="n">
-        <v>24.8</v>
+        <v>23.8085330357856</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>82.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>500.3</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
         <v>1</v>
       </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
       <c r="AE2" t="n">
         <v>0</v>
       </c>
       <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
         <v>1</v>
       </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
       <c r="AI2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="AK2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>166</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>91</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>52849965</v>
+        <v>53256014</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -758,78 +732,88 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>72.18069815195069</v>
+        <v>83.49075975359339</v>
       </c>
       <c r="D3" t="n">
+        <v>30.0408163265306</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>55</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>387</v>
+      </c>
+      <c r="I3" t="n">
+        <v>680</v>
+      </c>
+      <c r="J3" t="n">
+        <v>257</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1324</v>
+      </c>
+      <c r="L3" t="n">
+        <v>387</v>
+      </c>
+      <c r="M3" t="n">
+        <v>675</v>
+      </c>
+      <c r="N3" t="n">
+        <v>257</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1319</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
         <v>1</v>
       </c>
-      <c r="E3" t="n">
-        <v>27.7777777777778</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
+      <c r="U3" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="W3" t="n">
+        <v>29.60281941509253</v>
+      </c>
+      <c r="X3" t="n">
+        <v>29.11568115096522</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
         <v>1</v>
       </c>
-      <c r="H3" t="n">
-        <v>55</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="n">
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
         <v>1</v>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="n">
-        <v>158.73917</v>
-      </c>
-      <c r="P3" t="n">
-        <v>367.80267</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>85.01295</v>
-      </c>
-      <c r="R3" t="n">
-        <v>611.5549</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1</v>
-      </c>
-      <c r="X3" t="n">
-        <v>27.81884</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>89.7937</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>601.7905</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
@@ -847,19 +831,10 @@
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="AK3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>134</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>97</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
